--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487435_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487435_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4001</v>
+        <v>4.0493</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2646</v>
+        <v>2.5287</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1355</v>
+        <v>1.5207</v>
       </c>
       <c r="G2" t="n">
         <v>2.4442</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6241</v>
+        <v>0.2733</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2506</v>
+        <v>0.0135</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8746</v>
+        <v>0.2598</v>
       </c>
       <c r="V2" t="n">
         <v>1.3318</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7165</v>
+        <v>2.0651</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6777</v>
+        <v>2.5408</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0388</v>
+        <v>-0.4757</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3971</v>
+        <v>1.2525</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7857</v>
+        <v>0.9347</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.3178</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2793</v>
+        <v>2.1879</v>
       </c>
       <c r="K3" t="n">
-        <v>3.547</v>
+        <v>2.2898</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7323</v>
+        <v>-0.102</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8822</v>
+        <v>-0.9354</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7613</v>
+        <v>-1.3551</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1209</v>
+        <v>0.4197</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5668</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.3294</v>
+        <v>-2.1543</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2203</v>
+        <v>-0.2657</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5476</v>
+        <v>0.0741</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7679</v>
+        <v>-0.3398</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6659</v>
+        <v>1.2742</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2754</v>
+        <v>2.4332</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3905</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2978</v>
+        <v>1.605</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1744</v>
+        <v>0.78</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8767</v>
+        <v>0.825</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2525</v>
+        <v>2.3971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9347</v>
+        <v>1.7857</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3178</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1879</v>
+        <v>4.2793</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2898</v>
+        <v>3.547</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.102</v>
+        <v>0.7323</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9354</v>
+        <v>-1.8822</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3551</v>
+        <v>-1.7613</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4197</v>
+        <v>-0.1209</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1958</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1543</v>
+        <v>-3.3294</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0331</v>
+        <v>0.1088</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2923</v>
+        <v>-0.4452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7408</v>
+        <v>0.554</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2742</v>
+        <v>0.6659</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4332</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.159</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>M. SYLLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4362</v>
+        <v>-0.0003</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8501</v>
+        <v>0.2436</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2863</v>
+        <v>-0.2439</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3248</v>
+        <v>0.074</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0119</v>
+        <v>-0.5727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3129</v>
+        <v>0.6466</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0845</v>
+        <v>0.6177</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0037</v>
+        <v>-0.029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0808</v>
+        <v>0.6466</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4093</v>
+        <v>-0.5437</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0156</v>
+        <v>-0.5437</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3938</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.3087</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.0921</v>
+        <v>-0.1958</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1872</v>
+        <v>-0.2701</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6068</v>
+        <v>-0.1782</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5804</v>
+        <v>-0.0919</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8825</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SYLLA</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.027</v>
+        <v>-0.3017</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2436</v>
+        <v>-0.6405</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2706</v>
+        <v>0.3388</v>
       </c>
       <c r="G6" t="n">
-        <v>0.074</v>
+        <v>0.2256</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5727</v>
+        <v>0.2256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6466</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6177</v>
+        <v>0.0204</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.029</v>
+        <v>0.0204</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6466</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5437</v>
+        <v>0.2052</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5437</v>
+        <v>0.2052</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2968</v>
+        <v>0.1766</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1782</v>
+        <v>0.0429</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1186</v>
+        <v>0.1337</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2649</v>
+        <v>-0.3451</v>
       </c>
       <c r="E7" t="n">
         <v>0.2007</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4657</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9772</v>
@@ -1000,13 +1000,13 @@
         <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0711</v>
+        <v>-0.1513</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1071</v>
+        <v>0.0269</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4842</v>
+        <v>-0.4714</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7429</v>
+        <v>-1.4744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2587</v>
+        <v>1.003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2256</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2256</v>
+        <v>-1.0014</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.3537</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0204</v>
+        <v>-0.581</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0204</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2052</v>
+        <v>-0.0667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2052</v>
+        <v>-0.3396</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2729</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9792</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0059</v>
+        <v>-0.0979</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>0.0859</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0535</v>
+        <v>-0.1838</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2754</v>
+        <v>0.6659</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7295</v>
+        <v>-0.7508</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.679</v>
+        <v>-2.6094</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9495</v>
+        <v>1.8586</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.3248</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0014</v>
+        <v>-0.0119</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3537</v>
+        <v>-0.3129</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.581</v>
+        <v>1.0845</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.0037</v>
       </c>
       <c r="L9" t="n">
         <v>0.0808</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0667</v>
+        <v>-1.4093</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3396</v>
+        <v>-1.0156</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>-0.3938</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>-4.3087</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-5.0921</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3561</v>
+        <v>2.0003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1188</v>
+        <v>0.8475</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2373</v>
+        <v>1.1528</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6659</v>
+        <v>1.8825</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6659</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0805</v>
+        <v>-1.6322</v>
       </c>
       <c r="E10" t="n">
-        <v>0.102</v>
+        <v>-1.3581</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1825</v>
+        <v>-0.2741</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8285</v>
+        <v>-3.4964</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3736</v>
+        <v>-2.5261</v>
       </c>
       <c r="I10" t="n">
-        <v>1.545</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5014</v>
+        <v>-1.934</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4955</v>
+        <v>-0.6908</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9941</v>
+        <v>-1.2432</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3271</v>
+        <v>-1.5624</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8781</v>
+        <v>-1.8353</v>
       </c>
       <c r="O10" t="n">
-        <v>0.551</v>
+        <v>0.2729</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0856</v>
+        <v>0.6096</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7993</v>
+        <v>0.4964</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2864</v>
+        <v>0.1132</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7086</v>
+        <v>0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.174</v>
+        <v>-1.819</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8464</v>
+        <v>-0.7167</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3275</v>
+        <v>-1.1023</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4964</v>
+        <v>-0.8285</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5261</v>
+        <v>-2.3736</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9703000000000001</v>
+        <v>1.545</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.934</v>
+        <v>-0.5014</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6908</v>
+        <v>-1.4955</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2432</v>
+        <v>0.9941</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5624</v>
+        <v>-0.3271</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8353</v>
+        <v>-0.8781</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2729</v>
+        <v>0.551</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0678</v>
+        <v>0.3471</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0081</v>
+        <v>-0.0194</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0598</v>
+        <v>0.3666</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2754</v>
+        <v>-2.7086</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.034</v>
+        <v>-3.4003</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9314</v>
+        <v>-2.565</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1026</v>
+        <v>-0.8353</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0724</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1782</v>
+        <v>0.4555</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3517</v>
+        <v>0.0147</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1735</v>
+        <v>0.4408</v>
       </c>
       <c r="V12" t="n">
         <v>0.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.7552</v>
+        <v>-7.4005</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.377</v>
+        <v>-3.3966</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3782</v>
+        <v>-4.0039</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2436</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7121</v>
+        <v>0.6425</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7963</v>
+        <v>0.1841</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0842</v>
+        <v>0.4585</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4908</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.698699999999999</v>
+        <v>-8.401899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.763799999999999</v>
+        <v>-6.466900000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-1.935</v>
@@ -1513,16 +1513,16 @@
         <v>-5.1972</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7758</v>
+        <v>-5.775800000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5784000000000002</v>
+        <v>0.5783999999999998</v>
       </c>
       <c r="J14" t="n">
         <v>7.2605</v>
       </c>
       <c r="K14" t="n">
-        <v>8.124299999999998</v>
+        <v>8.124300000000002</v>
       </c>
       <c r="L14" t="n">
         <v>-0.8640000000000003</v>
@@ -1546,16 +1546,16 @@
         <v>14.6886</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5317</v>
+        <v>3.8287</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6410999999999998</v>
+        <v>0.9381000000000003</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8907</v>
+        <v>2.8908</v>
       </c>
       <c r="V14" t="n">
-        <v>1.779999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
         <v>8.8368</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6662</v>
+        <v>8.194699999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2794</v>
+        <v>6.8934</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3868</v>
+        <v>1.3013</v>
       </c>
       <c r="G15" t="n">
         <v>3.3104</v>
@@ -1624,13 +1624,13 @@
         <v>4.7004</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.523</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3968</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1262</v>
+        <v>-0.2117</v>
       </c>
       <c r="V15" t="n">
         <v>4.5079</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0451</v>
+        <v>7.2264</v>
       </c>
       <c r="E16" t="n">
-        <v>3.848</v>
+        <v>5.1565</v>
       </c>
       <c r="F16" t="n">
-        <v>2.197</v>
+        <v>2.0699</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6585</v>
+        <v>1.8028</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7738</v>
+        <v>-0.4256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1153</v>
+        <v>2.2284</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4533</v>
+        <v>3.4653</v>
       </c>
       <c r="K16" t="n">
-        <v>6.332</v>
+        <v>1.6774</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1212</v>
+        <v>1.7879</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7948</v>
+        <v>-1.6625</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5582</v>
+        <v>-2.103</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2366</v>
+        <v>0.4405</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>3.917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.3294</v>
+        <v>-0.1958</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3087</v>
+        <v>4.1128</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5896</v>
+        <v>-0.901</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1124</v>
+        <v>-1.0392</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4772</v>
+        <v>0.1382</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.1822</v>
+        <v>2.4077</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.3882</v>
+        <v>2.9263</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.794</v>
+        <v>-0.5187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6048</v>
+        <v>3.6213</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2355</v>
+        <v>1.392</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3693</v>
+        <v>2.2293</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8028</v>
+        <v>4.6585</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4256</v>
+        <v>4.7738</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2284</v>
+        <v>-0.1153</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4653</v>
+        <v>6.4533</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6774</v>
+        <v>6.332</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7879</v>
+        <v>0.1212</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6625</v>
+        <v>-1.7948</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.103</v>
+        <v>-1.5582</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4405</v>
+        <v>-0.2366</v>
       </c>
       <c r="P17" t="n">
-        <v>3.917</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1958</v>
+        <v>-3.3294</v>
       </c>
       <c r="R17" t="n">
-        <v>4.1128</v>
+        <v>4.3087</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5226</v>
+        <v>1.1658</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.9603</v>
+        <v>0.6563</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5624</v>
+        <v>0.5095</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4077</v>
+        <v>-3.1822</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9263</v>
+        <v>-2.3882</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5187</v>
+        <v>-0.794</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5602</v>
+        <v>2.2332</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.587</v>
+        <v>-0.973</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1471</v>
+        <v>3.2062</v>
       </c>
       <c r="G18" t="n">
         <v>2.2143</v>
@@ -1858,13 +1858,13 @@
         <v>4.7004</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8601</v>
+        <v>-0.187</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2186</v>
+        <v>-0.6046</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3585</v>
+        <v>0.4176</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1857</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2615</v>
+        <v>-1.137</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4533</v>
+        <v>-1.2486</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1918</v>
+        <v>0.1116</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0707</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.4154</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5346</v>
+        <v>-0.3299</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0052</v>
+        <v>-0.0854</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4344</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PETERS</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2374</v>
+        <v>-2.4843</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7577</v>
+        <v>-2.2124</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5203</v>
+        <v>-0.2719</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.724</v>
+        <v>-1.3035</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1886</v>
+        <v>-0.2171</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5354</v>
+        <v>-1.0864</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6677</v>
+        <v>-1.9242</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6677</v>
+        <v>-0.5597</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.3645</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0563</v>
+        <v>0.6208</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4791</v>
+        <v>0.3427</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5354</v>
+        <v>0.2781</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5875</v>
+        <v>0.5875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0741</v>
+        <v>-0.5518</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8893</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1849</v>
+        <v>-0.4595</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>R. PETERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8227</v>
+        <v>-3.2967</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4171</v>
+        <v>-3.5764</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4056</v>
+        <v>0.2797</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3035</v>
+        <v>-2.724</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2171</v>
+        <v>-2.1886</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0864</v>
+        <v>-0.5354</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9242</v>
+        <v>-2.6677</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5597</v>
+        <v>-2.6677</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3645</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6208</v>
+        <v>-0.0563</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3427</v>
+        <v>0.4791</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2781</v>
+        <v>-0.5354</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5875</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8901</v>
+        <v>0.0149</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.297</v>
+        <v>0.0706</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5931</v>
+        <v>-0.0557</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.856</v>
+        <v>-4.2944</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.213</v>
+        <v>-3.4966</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.643</v>
+        <v>-0.7978</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6907</v>
@@ -2170,13 +2170,13 @@
         <v>2.546</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8597</v>
+        <v>-0.2982</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.485</v>
+        <v>-0.7687</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6253</v>
+        <v>0.4705</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6765</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.698700000000001</v>
+        <v>10.0632</v>
       </c>
       <c r="E23" t="n">
-        <v>1.934799999999999</v>
+        <v>1.934900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>6.7637</v>
+        <v>8.128299999999999</v>
       </c>
       <c r="G23" t="n">
         <v>5.197100000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>5.775599999999999</v>
+        <v>5.775600000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-0.5782999999999996</v>
@@ -2233,10 +2233,10 @@
         <v>-7.2605</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.124500000000001</v>
+        <v>-8.124499999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8639</v>
+        <v>0.8638999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>8.813099999999999</v>
@@ -2248,13 +2248,13 @@
         <v>23.5019</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.531600000000001</v>
+        <v>-2.1672</v>
       </c>
       <c r="T23" t="n">
         <v>-2.8906</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.641</v>
+        <v>0.7234999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.779799999999999</v>
